--- a/Report samples/Rainfall 2024 vs 2025 up to Dec 2025.xlsx
+++ b/Report samples/Rainfall 2024 vs 2025 up to Dec 2025.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KEVIN\2025\3. MONTHLY HARVESTING &amp; MANURING REPORT\12. Dec 2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DEMO\2025\3. MONTHLY HARVESTING &amp; MANURING REPORT\12. Dec 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146078EE-F479-4D5B-A5FF-000B308140B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
